--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HamroAI\HamroAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D78E827-483F-4C25-89E6-AF1ACC0C5AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731BB87E-3B68-42AA-A4BF-C2CC8EDE7319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>EVEREST-NER</t>
   </si>
@@ -52,6 +52,42 @@
   </si>
   <si>
     <t>txt</t>
+  </si>
+  <si>
+    <t>IRISNEPAL</t>
+  </si>
+  <si>
+    <t>OSCAR Corpus (Nepali subset)</t>
+  </si>
+  <si>
+    <t>Wikipedia Nepali dump</t>
+  </si>
+  <si>
+    <t>Mozilla Common Voice</t>
+  </si>
+  <si>
+    <t>OPENSLR Nepali dataset</t>
+  </si>
+  <si>
+    <t>10.1 GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Text corpus</t>
+  </si>
+  <si>
+    <t>Web-crawled text</t>
+  </si>
+  <si>
+    <t>Encyclopedia text</t>
+  </si>
+  <si>
+    <t>82.8 MB</t>
+  </si>
+  <si>
+    <t>Speech data(100k+ clips)</t>
+  </si>
+  <si>
+    <t>Speech data (400+ hours)</t>
   </si>
 </sst>
 </file>
@@ -439,7 +475,9 @@
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -447,16 +485,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -464,16 +508,22 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>3.8</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -481,16 +531,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -501,13 +557,17 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -518,7 +578,9 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -712,16 +774,52 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="L9:O9"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="I17:K17"/>
@@ -738,56 +836,21 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="I13:K13"/>
     <mergeCell ref="I14:K14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="L9:O9"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="L14:O14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{72167E12-76A3-4177-B43C-7E613E60C3D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>